--- a/word-from-root/report/history/keyword-table-20260710-132202.xlsx
+++ b/word-from-root/report/history/keyword-table-20260710-132202.xlsx
@@ -54,12 +54,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,8 +620,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -685,408 +696,503 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>59.414634</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>59.414634</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>2800.0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this year</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this year</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>14.055882</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>810</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>14.055882</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>810.0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>what movies come out this year</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>what movies come out this year</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>10.357143</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>10.357143</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this summer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this summer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>10.24</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>what movie came out this year</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>what movie came out this year | what movies came out this year</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>what movie came out this year
+what movies came out this year</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>10.208183</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>580</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>42.103448</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0.741034</v>
-      </c>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>10.208183</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>580.0</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>42.103448</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>0.741034</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>what movies came out this weekend</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>what movies came out this weekend</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>8.035714</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>450</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>8.035714</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>450.0</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this month</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this month</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>7.327273</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>520</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>7.327273</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>520.0</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>what movies come out this weekend</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>what movies come out this weekend</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>3.980488</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>3.980488</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>what movies come out this month</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>what movies come out this month</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>3.921429</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3.921429</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>what new movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>what new movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0.278049</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0.278049</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>what movie is this</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>what movie is this | what is this movie | what movies is this</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>what movie is this
+what is this movie
+what movies is this</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="3" t="n">
-        <v>7710</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>38.92607</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L12" s="4" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>7710.0</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>38.92607</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>what movie is this picture from</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>what movie is this picture from</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L13" s="4" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L13"/>

--- a/word-from-root/report/history/keyword-table-20260710-132202.xlsx
+++ b/word-from-root/report/history/keyword-table-20260710-132202.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$13</definedName>
@@ -34,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -65,7 +75,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,16 +640,16 @@
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,52 +665,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score(simWindowVolume*cpc/kd)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sim)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sim)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sim)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sem)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sem)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sem)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>gefeiKD</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sourcePresence(SIM/SEM)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>score(simWindowVolume*cpc/kd)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sim)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sim)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sim)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sem)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sem)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sem)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>gefeiKD</t>
         </is>
       </c>
     </row>
@@ -702,40 +721,32 @@
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>59.414634</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>59.414634</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2800.0</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -744,40 +755,32 @@
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>14.055882</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>810</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this year</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>14.055882</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>810.0</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -786,40 +789,32 @@
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>10.357143</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>what movies come out this year</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>10.357143</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -828,40 +823,32 @@
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this summer</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>10.24</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>320.0</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -870,41 +857,33 @@
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>10.208183</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>580</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>42.103448</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.741034</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>what movie came out this year
 what movies came out this year</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>10.208183</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>580.0</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>42.103448</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>0.741034</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -913,40 +892,32 @@
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>8.035714</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>what movies came out this weekend</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>8.035714</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>450.0</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -955,40 +926,32 @@
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>7.327273</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>what movies are coming out this month</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>7.327273</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>520.0</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -997,40 +960,32 @@
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>3.980488</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>what movies come out this weekend</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>3.980488</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>340.0</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1039,40 +994,32 @@
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>3.921429</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>what movies come out this month</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>3.921429</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>270.0</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1081,40 +1028,32 @@
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>0.278049</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>what new movies are coming out this weekend</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>0.278049</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1123,38 +1062,32 @@
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>7710</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>38.92607</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>what movie is this
 what is this movie
 what movies is this</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>7710.0</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>38.92607</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1163,36 +1096,30 @@
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>260</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>what movie is this picture from</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>260.0</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L13"/>
